--- a/outputs/Block6C_Electoral_Risk.xlsx
+++ b/outputs/Block6C_Electoral_Risk.xlsx
@@ -40,10 +40,10 @@
     <t>Range-Based Estimate</t>
   </si>
   <si>
-    <t>Based on the national House Monte Carlo distribution and nested historical error.</t>
-  </si>
-  <si>
-    <t>Based on state-level Senate simulations calibrated with historical polling error.</t>
+    <t>Derived only from the same 435 district simulations; joint-mode central and joint distribution centers are reported separately.</t>
+  </si>
+  <si>
+    <t>Derived only from the same 11 monitored state-race simulations plus fixed seats; margin sensitivity is audited.</t>
   </si>
   <si>
     <t>Based only on simulated popular vote uncertainty.</t>
